--- a/crosswalk/xlsx/grade-08-us-history-geography__primary-source-crosswalk.xlsx
+++ b/crosswalk/xlsx/grade-08-us-history-geography__primary-source-crosswalk.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -12417,7 +12417,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -13210,7 +13210,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
